--- a/data/raw/sales/Week 17/Audio_Array/other_channels.xlsx
+++ b/data/raw/sales/Week 17/Audio_Array/other_channels.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\Week 17\Week 17\raw\sales\Week 17\Audio_Array\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\sales\Week 17\Audio_Array\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6352B8C-46CE-487C-A237-7364FD98A582}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18B8C8F5-D80D-48B1-A35D-33D86D5110FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="D2C - Audio Array" sheetId="4" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="652" uniqueCount="373">
   <si>
     <t>SKU</t>
   </si>
@@ -439,9 +439,6 @@
   </si>
   <si>
     <t>Audio Array</t>
-  </si>
-  <si>
-    <t>AI-04</t>
   </si>
   <si>
     <t>FBA79983</t>
@@ -1171,7 +1168,7 @@
   <numFmts count="1">
     <numFmt numFmtId="8" formatCode="&quot;₹&quot;\ #,##0.00;[Red]&quot;₹&quot;\ \-#,##0.00"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1209,12 +1206,6 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
@@ -1326,7 +1317,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1362,40 +1353,31 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1405,7 +1387,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1683,319 +1665,319 @@
       <c r="AA1" s="4"/>
     </row>
     <row r="2" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="17">
+      <c r="D2" s="14">
         <v>3</v>
       </c>
-      <c r="E2" s="17">
+      <c r="E2" s="14">
         <v>7273.7290000000003</v>
       </c>
-      <c r="F2" s="17" t="s">
+      <c r="F2" s="14" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="3" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="C3" s="17" t="s">
-        <v>292</v>
-      </c>
-      <c r="D3" s="17">
+      <c r="C3" s="14" t="s">
+        <v>291</v>
+      </c>
+      <c r="D3" s="14">
         <v>2</v>
       </c>
-      <c r="E3" s="17">
+      <c r="E3" s="14">
         <v>8622.0339999999997</v>
       </c>
-      <c r="F3" s="17" t="s">
+      <c r="F3" s="14" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="4" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="C4" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="17">
+      <c r="D4" s="14">
         <v>2</v>
       </c>
-      <c r="E4" s="17">
+      <c r="E4" s="14">
         <v>8532.2029999999995</v>
       </c>
-      <c r="F4" s="17" t="s">
+      <c r="F4" s="14" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="5" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="C5" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="D5" s="17">
+      <c r="D5" s="14">
         <v>2</v>
       </c>
-      <c r="E5" s="17">
+      <c r="E5" s="14">
         <v>3052.5419999999999</v>
       </c>
-      <c r="F5" s="17" t="s">
+      <c r="F5" s="14" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="6" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="C6" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="17">
+      <c r="D6" s="14">
         <v>1</v>
       </c>
-      <c r="E6" s="22">
+      <c r="E6" s="19">
         <v>4580.5079999999998</v>
       </c>
-      <c r="F6" s="17" t="s">
+      <c r="F6" s="14" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="7" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="14" t="s">
+        <v>276</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>278</v>
+      </c>
+      <c r="C7" s="14" t="s">
         <v>277</v>
       </c>
-      <c r="B7" s="17" t="s">
-        <v>279</v>
-      </c>
-      <c r="C7" s="17" t="s">
-        <v>278</v>
-      </c>
-      <c r="D7" s="17">
+      <c r="D7" s="14">
         <v>1</v>
       </c>
-      <c r="E7" s="22">
+      <c r="E7" s="19">
         <v>1481.356</v>
       </c>
-      <c r="F7" s="17" t="s">
+      <c r="F7" s="14" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="8" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="17" t="s">
+      <c r="A8" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="B8" s="17" t="s">
-        <v>168</v>
-      </c>
-      <c r="C8" s="17" t="s">
+      <c r="B8" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="C8" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="D8" s="17">
+      <c r="D8" s="14">
         <v>1</v>
       </c>
-      <c r="E8" s="22">
+      <c r="E8" s="19">
         <v>2244.915</v>
       </c>
-      <c r="F8" s="17" t="s">
+      <c r="F8" s="14" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="9" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="C9" s="17" t="s">
+      <c r="C9" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="D9" s="17">
+      <c r="D9" s="14">
         <v>1</v>
       </c>
-      <c r="E9" s="22">
+      <c r="E9" s="19">
         <v>2881.3560000000002</v>
       </c>
-      <c r="F9" s="17" t="s">
+      <c r="F9" s="14" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="10" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="17" t="s">
+      <c r="A10" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="B10" s="17" t="s">
+      <c r="B10" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="C10" s="17" t="s">
+      <c r="C10" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="D10" s="17">
+      <c r="D10" s="14">
         <v>2</v>
       </c>
-      <c r="E10" s="22">
+      <c r="E10" s="19">
         <v>2783.0509999999999</v>
       </c>
-      <c r="F10" s="17" t="s">
+      <c r="F10" s="14" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="11" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="C11" s="17" t="s">
+      <c r="C11" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="D11" s="17">
+      <c r="D11" s="14">
         <v>1</v>
       </c>
-      <c r="E11" s="22">
+      <c r="E11" s="19">
         <v>1077.1189999999999</v>
       </c>
-      <c r="F11" s="17" t="s">
+      <c r="F11" s="14" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="12" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="17" t="s">
+      <c r="A12" s="14" t="s">
+        <v>366</v>
+      </c>
+      <c r="B12" s="14" t="s">
         <v>367</v>
       </c>
-      <c r="B12" s="17" t="s">
+      <c r="C12" s="14" t="s">
         <v>368</v>
       </c>
-      <c r="C12" s="17" t="s">
-        <v>369</v>
-      </c>
-      <c r="D12" s="17">
+      <c r="D12" s="14">
         <v>1</v>
       </c>
-      <c r="E12" s="22">
+      <c r="E12" s="19">
         <v>2738.9830000000002</v>
       </c>
-      <c r="F12" s="17" t="s">
+      <c r="F12" s="14" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="13" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="17" t="s">
+      <c r="A13" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="17" t="s">
+      <c r="B13" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="17" t="s">
+      <c r="C13" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="D13" s="17">
+      <c r="D13" s="14">
         <v>4</v>
       </c>
-      <c r="E13" s="22">
+      <c r="E13" s="19">
         <v>7284.7460000000001</v>
       </c>
-      <c r="F13" s="17" t="s">
+      <c r="F13" s="14" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="14" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="17" t="s">
+      <c r="A14" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="B14" s="17" t="s">
+      <c r="B14" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="C14" s="17" t="s">
-        <v>180</v>
-      </c>
-      <c r="D14" s="17">
+      <c r="C14" s="14" t="s">
+        <v>179</v>
+      </c>
+      <c r="D14" s="14">
         <v>1</v>
       </c>
-      <c r="E14" s="22">
+      <c r="E14" s="19">
         <v>1166.9490000000001</v>
       </c>
-      <c r="F14" s="17" t="s">
+      <c r="F14" s="14" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="23" t="s">
+      <c r="A15" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="B15" s="23" t="s">
+      <c r="B15" s="20" t="s">
         <v>125</v>
       </c>
-      <c r="C15" s="23" t="s">
+      <c r="C15" s="20" t="s">
         <v>124</v>
       </c>
-      <c r="D15" s="23">
+      <c r="D15" s="20">
         <v>1</v>
       </c>
-      <c r="E15" s="24">
+      <c r="E15" s="21">
         <v>1795.7629999999999</v>
       </c>
-      <c r="F15" s="23" t="s">
+      <c r="F15" s="20" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="16" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="23" t="s">
+      <c r="A16" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="B16" s="23" t="s">
+      <c r="B16" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="C16" s="23" t="s">
+      <c r="C16" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="D16" s="23">
+      <c r="D16" s="20">
         <v>5</v>
       </c>
-      <c r="E16" s="24">
+      <c r="E16" s="21">
         <v>8474.5759999999991</v>
       </c>
-      <c r="F16" s="23" t="s">
+      <c r="F16" s="20" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="23" t="s">
+      <c r="A17" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="B17" s="23" t="s">
+      <c r="B17" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="C17" s="23" t="s">
+      <c r="C17" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="D17" s="23">
+      <c r="D17" s="20">
         <v>1</v>
       </c>
-      <c r="E17" s="24">
+      <c r="E17" s="21">
         <v>7626.2709999999997</v>
       </c>
       <c r="F17" s="11" t="s">
@@ -2003,19 +1985,19 @@
       </c>
     </row>
     <row r="18" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="26" t="s">
+      <c r="A18" s="23" t="s">
         <v>90</v>
       </c>
-      <c r="B18" s="26" t="s">
+      <c r="B18" s="23" t="s">
         <v>91</v>
       </c>
-      <c r="C18" s="26" t="s">
+      <c r="C18" s="23" t="s">
         <v>96</v>
       </c>
-      <c r="D18" s="26">
+      <c r="D18" s="23">
         <v>2</v>
       </c>
-      <c r="E18" s="24">
+      <c r="E18" s="21">
         <v>6118.6440000000002</v>
       </c>
       <c r="F18" s="12" t="s">
@@ -2062,102 +2044,102 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="24" t="s">
+        <v>210</v>
+      </c>
+      <c r="B2" s="25" t="s">
+        <v>212</v>
+      </c>
+      <c r="C2" s="24" t="s">
         <v>211</v>
       </c>
-      <c r="B2" s="28" t="s">
-        <v>213</v>
-      </c>
-      <c r="C2" s="27" t="s">
-        <v>212</v>
-      </c>
-      <c r="D2" s="29">
+      <c r="D2" s="26">
         <v>2</v>
       </c>
-      <c r="E2" s="27">
+      <c r="E2" s="24">
         <v>4608.4750000000004</v>
       </c>
-      <c r="F2" s="27" t="s">
+      <c r="F2" s="24" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="27" t="s">
+      <c r="A3" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="27" t="s">
+      <c r="B3" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="C3" s="27" t="s">
+      <c r="C3" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="D3" s="27">
+      <c r="D3" s="24">
         <v>2</v>
       </c>
-      <c r="E3" s="27">
+      <c r="E3" s="24">
         <v>2592.373</v>
       </c>
-      <c r="F3" s="27" t="s">
+      <c r="F3" s="24" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="27" t="s">
+      <c r="A4" s="24" t="s">
         <v>116</v>
       </c>
-      <c r="B4" s="27" t="s">
+      <c r="B4" s="24" t="s">
         <v>118</v>
       </c>
-      <c r="C4" s="27" t="s">
+      <c r="C4" s="24" t="s">
         <v>117</v>
       </c>
-      <c r="D4" s="27">
+      <c r="D4" s="24">
         <v>1</v>
       </c>
-      <c r="E4" s="27">
+      <c r="E4" s="24">
         <v>1007.627</v>
       </c>
-      <c r="F4" s="27" t="s">
+      <c r="F4" s="24" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="27" t="s">
+      <c r="A5" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="27" t="s">
+      <c r="B5" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="27" t="s">
+      <c r="C5" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="27">
+      <c r="D5" s="24">
         <v>1</v>
       </c>
-      <c r="E5" s="27">
+      <c r="E5" s="24">
         <v>1655.932</v>
       </c>
-      <c r="F5" s="27" t="s">
+      <c r="F5" s="24" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="27" t="s">
+      <c r="A6" s="24" t="s">
         <v>95</v>
       </c>
-      <c r="B6" s="27" t="s">
+      <c r="B6" s="24" t="s">
         <v>97</v>
       </c>
-      <c r="C6" s="27" t="s">
+      <c r="C6" s="24" t="s">
         <v>96</v>
       </c>
-      <c r="D6" s="27">
+      <c r="D6" s="24">
         <v>1</v>
       </c>
-      <c r="E6" s="27">
+      <c r="E6" s="24">
         <v>2589.8310000000001</v>
       </c>
-      <c r="F6" s="27" t="s">
+      <c r="F6" s="24" t="s">
         <v>132</v>
       </c>
     </row>
@@ -2168,7 +2150,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:X923"/>
+  <dimension ref="A1:X916"/>
   <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.109375" customWidth="1"/>
@@ -2219,146 +2201,165 @@
       <c r="X1" s="4"/>
     </row>
     <row r="2" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="B2" s="14" t="s">
+      <c r="A2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B2" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" t="s">
         <v>19</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="D2" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="15">
-        <v>2</v>
-      </c>
-      <c r="F2" s="16">
-        <v>8642.3700000000008</v>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>4321</v>
       </c>
     </row>
     <row r="3" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="B3" s="14" t="s">
+      <c r="A3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B3" t="s">
         <v>92</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" t="s">
         <v>94</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="D3" t="s">
         <v>93</v>
       </c>
-      <c r="E3" s="15">
-        <v>21</v>
-      </c>
-      <c r="F3" s="16">
-        <v>33795.760000000002</v>
+      <c r="E3">
+        <v>17</v>
+      </c>
+      <c r="F3">
+        <v>32401</v>
       </c>
     </row>
     <row r="4" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="B4" s="14" t="s">
+      <c r="A4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B4" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="D4" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="15">
+      <c r="E4">
+        <v>7</v>
+      </c>
+      <c r="F4">
+        <v>16011</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>132</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>132</v>
+      </c>
+      <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6">
+        <v>8</v>
+      </c>
+      <c r="F6">
+        <v>23851</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>132</v>
+      </c>
+      <c r="B7" t="s">
+        <v>126</v>
+      </c>
+      <c r="C7" t="s">
+        <v>128</v>
+      </c>
+      <c r="D7" t="s">
+        <v>127</v>
+      </c>
+      <c r="E7">
         <v>5</v>
       </c>
-      <c r="F4" s="16">
-        <v>11266.95</v>
-      </c>
-    </row>
-    <row r="5" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>133</v>
-      </c>
-      <c r="E5" s="15">
-        <v>1</v>
-      </c>
-      <c r="F5" s="16">
-        <v>4066.95</v>
-      </c>
-    </row>
-    <row r="6" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="B6" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" s="15">
-        <v>4</v>
-      </c>
-      <c r="F6" s="16">
-        <v>11925.42</v>
-      </c>
-    </row>
-    <row r="7" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>126</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>128</v>
-      </c>
-      <c r="D7" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="E7" s="15">
-        <v>3</v>
-      </c>
-      <c r="F7" s="16">
-        <v>4022.88</v>
+      <c r="F7">
+        <v>8047</v>
       </c>
     </row>
     <row r="8" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="B8" s="14" t="s">
+      <c r="A8" t="s">
+        <v>132</v>
+      </c>
+      <c r="B8" t="s">
         <v>72</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="C8" t="s">
         <v>74</v>
       </c>
-      <c r="D8" s="14" t="s">
+      <c r="D8" t="s">
         <v>73</v>
       </c>
-      <c r="E8" s="15">
+      <c r="E8">
         <v>0</v>
       </c>
-      <c r="F8" s="16">
+      <c r="F8">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="9" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>132</v>
+      </c>
+      <c r="B9" t="s">
+        <v>116</v>
+      </c>
+      <c r="C9" t="s">
+        <v>118</v>
+      </c>
+      <c r="D9" t="s">
+        <v>117</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+    </row>
     <row r="10" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="11" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="12" spans="1:24" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -3266,13 +3267,6 @@
     <row r="914" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="915" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="916" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="917" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="918" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="919" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="920" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="921" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="922" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="923" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -3347,12 +3341,12 @@
         <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E2" t="s">
         <v>132</v>
       </c>
-      <c r="F2" s="25">
+      <c r="F2" s="22">
         <v>377804.25</v>
       </c>
       <c r="G2">
@@ -3370,12 +3364,12 @@
         <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E3" t="s">
         <v>132</v>
       </c>
-      <c r="F3" s="25">
+      <c r="F3" s="22">
         <v>375554.76</v>
       </c>
       <c r="G3">
@@ -3393,12 +3387,12 @@
         <v>16</v>
       </c>
       <c r="D4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E4" t="s">
         <v>132</v>
       </c>
-      <c r="F4" s="25">
+      <c r="F4" s="22">
         <v>160151.76999999999</v>
       </c>
       <c r="G4">
@@ -3416,12 +3410,12 @@
         <v>19</v>
       </c>
       <c r="D5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E5" t="s">
         <v>132</v>
       </c>
-      <c r="F5" s="25">
+      <c r="F5" s="22">
         <v>129635.6</v>
       </c>
       <c r="G5">
@@ -3439,12 +3433,12 @@
         <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E6" t="s">
         <v>132</v>
       </c>
-      <c r="F6" s="25">
+      <c r="F6" s="22">
         <v>110114.36</v>
       </c>
       <c r="G6">
@@ -3453,21 +3447,21 @@
     </row>
     <row r="7" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>142</v>
+      </c>
+      <c r="B7" t="s">
         <v>143</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>144</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>145</v>
       </c>
-      <c r="D7" t="s">
-        <v>146</v>
-      </c>
       <c r="E7" t="s">
         <v>132</v>
       </c>
-      <c r="F7" s="25">
+      <c r="F7" s="22">
         <v>65244.959999999999</v>
       </c>
       <c r="G7">
@@ -3485,12 +3479,12 @@
         <v>28</v>
       </c>
       <c r="D8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E8" t="s">
         <v>132</v>
       </c>
-      <c r="F8" s="25">
+      <c r="F8" s="22">
         <v>58127.05</v>
       </c>
       <c r="G8">
@@ -3508,12 +3502,12 @@
         <v>25</v>
       </c>
       <c r="D9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E9" t="s">
         <v>132</v>
       </c>
-      <c r="F9" s="25">
+      <c r="F9" s="22">
         <v>53679.6</v>
       </c>
       <c r="G9">
@@ -3531,12 +3525,12 @@
         <v>56</v>
       </c>
       <c r="D10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E10" t="s">
         <v>132</v>
       </c>
-      <c r="F10" s="25">
+      <c r="F10" s="22">
         <v>52867.839999999997</v>
       </c>
       <c r="G10">
@@ -3554,12 +3548,12 @@
         <v>37</v>
       </c>
       <c r="D11" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E11" t="s">
         <v>132</v>
       </c>
-      <c r="F11" s="25">
+      <c r="F11" s="22">
         <v>51473.72</v>
       </c>
       <c r="G11">
@@ -3577,12 +3571,12 @@
         <v>31</v>
       </c>
       <c r="D12" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E12" t="s">
         <v>132</v>
       </c>
-      <c r="F12" s="25">
+      <c r="F12" s="22">
         <v>50833.919999999998</v>
       </c>
       <c r="G12">
@@ -3591,21 +3585,21 @@
     </row>
     <row r="13" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>151</v>
+      </c>
+      <c r="B13" t="s">
         <v>152</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>153</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>154</v>
       </c>
-      <c r="D13" t="s">
-        <v>155</v>
-      </c>
       <c r="E13" t="s">
         <v>132</v>
       </c>
-      <c r="F13" s="25">
+      <c r="F13" s="22">
         <v>50702.6</v>
       </c>
       <c r="G13">
@@ -3623,12 +3617,12 @@
         <v>53</v>
       </c>
       <c r="D14" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E14" t="s">
         <v>132</v>
       </c>
-      <c r="F14" s="25">
+      <c r="F14" s="22">
         <v>36587.160000000003</v>
       </c>
       <c r="G14">
@@ -3637,21 +3631,21 @@
     </row>
     <row r="15" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>156</v>
+      </c>
+      <c r="B15" t="s">
         <v>157</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>158</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>159</v>
       </c>
-      <c r="D15" t="s">
-        <v>160</v>
-      </c>
       <c r="E15" t="s">
         <v>132</v>
       </c>
-      <c r="F15" s="25">
+      <c r="F15" s="22">
         <v>33894.92</v>
       </c>
       <c r="G15">
@@ -3660,21 +3654,21 @@
     </row>
     <row r="16" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>160</v>
+      </c>
+      <c r="B16" t="s">
         <v>161</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>162</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>163</v>
       </c>
-      <c r="D16" t="s">
-        <v>164</v>
-      </c>
       <c r="E16" t="s">
         <v>132</v>
       </c>
-      <c r="F16" s="25">
+      <c r="F16" s="22">
         <v>28868.9</v>
       </c>
       <c r="G16">
@@ -3692,12 +3686,12 @@
         <v>45</v>
       </c>
       <c r="D17" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E17" t="s">
         <v>132</v>
       </c>
-      <c r="F17" s="25">
+      <c r="F17" s="22">
         <v>27961</v>
       </c>
       <c r="G17">
@@ -3715,12 +3709,12 @@
         <v>40</v>
       </c>
       <c r="D18" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E18" t="s">
         <v>132</v>
       </c>
-      <c r="F18" s="25">
+      <c r="F18" s="22">
         <v>25757.57</v>
       </c>
       <c r="G18">
@@ -3738,12 +3732,12 @@
         <v>50</v>
       </c>
       <c r="D19" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E19" t="s">
         <v>132</v>
       </c>
-      <c r="F19" s="25">
+      <c r="F19" s="22">
         <v>24150</v>
       </c>
       <c r="G19">
@@ -3758,15 +3752,15 @@
         <v>42</v>
       </c>
       <c r="C20" t="s">
+        <v>167</v>
+      </c>
+      <c r="D20" t="s">
         <v>168</v>
       </c>
-      <c r="D20" t="s">
-        <v>169</v>
-      </c>
       <c r="E20" t="s">
         <v>132</v>
       </c>
-      <c r="F20" s="25">
+      <c r="F20" s="22">
         <v>23295.8</v>
       </c>
       <c r="G20">
@@ -3784,12 +3778,12 @@
         <v>59</v>
       </c>
       <c r="D21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E21" t="s">
         <v>132</v>
       </c>
-      <c r="F21" s="25">
+      <c r="F21" s="22">
         <v>21866.99</v>
       </c>
       <c r="G21">
@@ -3807,12 +3801,12 @@
         <v>34</v>
       </c>
       <c r="D22" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E22" t="s">
         <v>132</v>
       </c>
-      <c r="F22" s="25">
+      <c r="F22" s="22">
         <v>21010.17</v>
       </c>
       <c r="G22">
@@ -3821,21 +3815,21 @@
     </row>
     <row r="23" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
+        <v>171</v>
+      </c>
+      <c r="B23" t="s">
         <v>172</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
         <v>173</v>
       </c>
-      <c r="C23" t="s">
+      <c r="D23" t="s">
         <v>174</v>
       </c>
-      <c r="D23" t="s">
-        <v>175</v>
-      </c>
       <c r="E23" t="s">
         <v>132</v>
       </c>
-      <c r="F23" s="25">
+      <c r="F23" s="22">
         <v>19659.32</v>
       </c>
       <c r="G23">
@@ -3847,18 +3841,18 @@
         <v>86</v>
       </c>
       <c r="B24" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C24" t="s">
         <v>87</v>
       </c>
       <c r="D24" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E24" t="s">
         <v>132</v>
       </c>
-      <c r="F24" s="25">
+      <c r="F24" s="22">
         <v>18634.740000000002</v>
       </c>
       <c r="G24">
@@ -3876,12 +3870,12 @@
         <v>74</v>
       </c>
       <c r="D25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E25" t="s">
         <v>132</v>
       </c>
-      <c r="F25" s="25">
+      <c r="F25" s="22">
         <v>18137.28</v>
       </c>
       <c r="G25">
@@ -3899,12 +3893,12 @@
         <v>62</v>
       </c>
       <c r="D26" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E26" t="s">
         <v>132</v>
       </c>
-      <c r="F26" s="25">
+      <c r="F26" s="22">
         <v>17771.189999999999</v>
       </c>
       <c r="G26">
@@ -3916,18 +3910,18 @@
         <v>46</v>
       </c>
       <c r="B27" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C27" t="s">
         <v>47</v>
       </c>
       <c r="D27" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E27" t="s">
         <v>132</v>
       </c>
-      <c r="F27" s="25">
+      <c r="F27" s="22">
         <v>17273.7</v>
       </c>
       <c r="G27">
@@ -3945,12 +3939,12 @@
         <v>80</v>
       </c>
       <c r="D28" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E28" t="s">
         <v>132</v>
       </c>
-      <c r="F28" s="25">
+      <c r="F28" s="22">
         <v>16945.759999999998</v>
       </c>
       <c r="G28">
@@ -3959,21 +3953,21 @@
     </row>
     <row r="29" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
+        <v>182</v>
+      </c>
+      <c r="B29" t="s">
         <v>183</v>
       </c>
-      <c r="B29" t="s">
+      <c r="C29" t="s">
         <v>184</v>
       </c>
-      <c r="C29" t="s">
+      <c r="D29" t="s">
         <v>185</v>
       </c>
-      <c r="D29" t="s">
-        <v>186</v>
-      </c>
       <c r="E29" t="s">
         <v>132</v>
       </c>
-      <c r="F29" s="25">
+      <c r="F29" s="22">
         <v>16944.900000000001</v>
       </c>
       <c r="G29">
@@ -3991,12 +3985,12 @@
         <v>65</v>
       </c>
       <c r="D30" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E30" t="s">
         <v>132</v>
       </c>
-      <c r="F30" s="25">
+      <c r="F30" s="22">
         <v>16942.400000000001</v>
       </c>
       <c r="G30">
@@ -4005,21 +3999,21 @@
     </row>
     <row r="31" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
+        <v>187</v>
+      </c>
+      <c r="B31" t="s">
         <v>188</v>
       </c>
-      <c r="B31" t="s">
+      <c r="C31" t="s">
         <v>189</v>
       </c>
-      <c r="C31" t="s">
+      <c r="D31" t="s">
         <v>190</v>
       </c>
-      <c r="D31" t="s">
-        <v>191</v>
-      </c>
       <c r="E31" t="s">
         <v>132</v>
       </c>
-      <c r="F31" s="25">
+      <c r="F31" s="22">
         <v>16355.08</v>
       </c>
       <c r="G31">
@@ -4037,12 +4031,12 @@
         <v>68</v>
       </c>
       <c r="D32" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E32" t="s">
         <v>132</v>
       </c>
-      <c r="F32" s="25">
+      <c r="F32" s="22">
         <v>16260.96</v>
       </c>
       <c r="G32">
@@ -4051,21 +4045,21 @@
     </row>
     <row r="33" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
+        <v>192</v>
+      </c>
+      <c r="B33" t="s">
         <v>193</v>
       </c>
-      <c r="B33" t="s">
+      <c r="C33" t="s">
         <v>194</v>
       </c>
-      <c r="C33" t="s">
+      <c r="D33" t="s">
         <v>195</v>
       </c>
-      <c r="D33" t="s">
-        <v>196</v>
-      </c>
       <c r="E33" t="s">
         <v>132</v>
       </c>
-      <c r="F33" s="25">
+      <c r="F33" s="22">
         <v>14614.4</v>
       </c>
       <c r="G33">
@@ -4077,18 +4071,18 @@
         <v>88</v>
       </c>
       <c r="B34" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C34" t="s">
         <v>89</v>
       </c>
       <c r="D34" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E34" t="s">
         <v>132</v>
       </c>
-      <c r="F34" s="25">
+      <c r="F34" s="22">
         <v>13217.79</v>
       </c>
       <c r="G34">
@@ -4097,21 +4091,21 @@
     </row>
     <row r="35" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>198</v>
+      </c>
+      <c r="B35" t="s">
         <v>199</v>
       </c>
-      <c r="B35" t="s">
+      <c r="C35" t="s">
         <v>200</v>
       </c>
-      <c r="C35" t="s">
+      <c r="D35" t="s">
         <v>201</v>
       </c>
-      <c r="D35" t="s">
-        <v>202</v>
-      </c>
       <c r="E35" t="s">
         <v>132</v>
       </c>
-      <c r="F35" s="25">
+      <c r="F35" s="22">
         <v>13216.96</v>
       </c>
       <c r="G35">
@@ -4120,21 +4114,21 @@
     </row>
     <row r="36" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
+        <v>202</v>
+      </c>
+      <c r="B36" t="s">
         <v>203</v>
       </c>
-      <c r="B36" t="s">
+      <c r="C36" t="s">
         <v>204</v>
       </c>
-      <c r="C36" t="s">
+      <c r="D36" t="s">
         <v>205</v>
       </c>
-      <c r="D36" t="s">
-        <v>206</v>
-      </c>
       <c r="E36" t="s">
         <v>132</v>
       </c>
-      <c r="F36" s="25">
+      <c r="F36" s="22">
         <v>13209.3</v>
       </c>
       <c r="G36">
@@ -4143,21 +4137,21 @@
     </row>
     <row r="37" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
+        <v>206</v>
+      </c>
+      <c r="B37" t="s">
         <v>207</v>
       </c>
-      <c r="B37" t="s">
+      <c r="C37" t="s">
         <v>208</v>
       </c>
-      <c r="C37" t="s">
+      <c r="D37" t="s">
         <v>209</v>
       </c>
-      <c r="D37" t="s">
-        <v>210</v>
-      </c>
       <c r="E37" t="s">
         <v>132</v>
       </c>
-      <c r="F37" s="25">
+      <c r="F37" s="22">
         <v>12774.73</v>
       </c>
       <c r="G37">
@@ -4166,21 +4160,21 @@
     </row>
     <row r="38" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>210</v>
+      </c>
+      <c r="B38" t="s">
         <v>211</v>
       </c>
-      <c r="B38" t="s">
+      <c r="C38" t="s">
         <v>212</v>
       </c>
-      <c r="C38" t="s">
+      <c r="D38" t="s">
         <v>213</v>
       </c>
-      <c r="D38" t="s">
-        <v>214</v>
-      </c>
       <c r="E38" t="s">
         <v>132</v>
       </c>
-      <c r="F38" s="25">
+      <c r="F38" s="22">
         <v>12099.99</v>
       </c>
       <c r="G38">
@@ -4198,12 +4192,12 @@
         <v>71</v>
       </c>
       <c r="D39" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E39" t="s">
         <v>132</v>
       </c>
-      <c r="F39" s="25">
+      <c r="F39" s="22">
         <v>11946.6</v>
       </c>
       <c r="G39">
@@ -4212,21 +4206,21 @@
     </row>
     <row r="40" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
+        <v>215</v>
+      </c>
+      <c r="B40" t="s">
         <v>216</v>
       </c>
-      <c r="B40" t="s">
+      <c r="C40" t="s">
         <v>217</v>
       </c>
-      <c r="C40" t="s">
+      <c r="D40" t="s">
         <v>218</v>
       </c>
-      <c r="D40" t="s">
-        <v>219</v>
-      </c>
       <c r="E40" t="s">
         <v>132</v>
       </c>
-      <c r="F40" s="25">
+      <c r="F40" s="22">
         <v>11862.72</v>
       </c>
       <c r="G40">
@@ -4235,21 +4229,21 @@
     </row>
     <row r="41" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
+        <v>219</v>
+      </c>
+      <c r="B41" t="s">
         <v>220</v>
       </c>
-      <c r="B41" t="s">
+      <c r="C41" t="s">
         <v>221</v>
       </c>
-      <c r="C41" t="s">
+      <c r="D41" t="s">
         <v>222</v>
       </c>
-      <c r="D41" t="s">
-        <v>223</v>
-      </c>
       <c r="E41" t="s">
         <v>132</v>
       </c>
-      <c r="F41" s="25">
+      <c r="F41" s="22">
         <v>11793.22</v>
       </c>
       <c r="G41">
@@ -4258,21 +4252,21 @@
     </row>
     <row r="42" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
+        <v>223</v>
+      </c>
+      <c r="B42" t="s">
         <v>224</v>
       </c>
-      <c r="B42" t="s">
+      <c r="C42" t="s">
         <v>225</v>
       </c>
-      <c r="C42" t="s">
+      <c r="D42" t="s">
         <v>226</v>
       </c>
-      <c r="D42" t="s">
-        <v>227</v>
-      </c>
       <c r="E42" t="s">
         <v>132</v>
       </c>
-      <c r="F42" s="25">
+      <c r="F42" s="22">
         <v>11270.34</v>
       </c>
       <c r="G42">
@@ -4281,21 +4275,21 @@
     </row>
     <row r="43" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
+        <v>227</v>
+      </c>
+      <c r="B43" t="s">
         <v>228</v>
       </c>
-      <c r="B43" t="s">
+      <c r="C43" t="s">
         <v>229</v>
       </c>
-      <c r="C43" t="s">
+      <c r="D43" t="s">
         <v>230</v>
       </c>
-      <c r="D43" t="s">
-        <v>231</v>
-      </c>
       <c r="E43" t="s">
         <v>132</v>
       </c>
-      <c r="F43" s="25">
+      <c r="F43" s="22">
         <v>11265.24</v>
       </c>
       <c r="G43">
@@ -4313,12 +4307,12 @@
         <v>77</v>
       </c>
       <c r="D44" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E44" t="s">
         <v>132</v>
       </c>
-      <c r="F44" s="25">
+      <c r="F44" s="22">
         <v>10676.28</v>
       </c>
       <c r="G44">
@@ -4336,12 +4330,12 @@
         <v>125</v>
       </c>
       <c r="D45" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E45" t="s">
         <v>132</v>
       </c>
-      <c r="F45" s="25">
+      <c r="F45" s="22">
         <v>10164.4</v>
       </c>
       <c r="G45">
@@ -4350,21 +4344,21 @@
     </row>
     <row r="46" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
+        <v>233</v>
+      </c>
+      <c r="B46" t="s">
         <v>234</v>
       </c>
-      <c r="B46" t="s">
+      <c r="C46" t="s">
         <v>235</v>
       </c>
-      <c r="C46" t="s">
+      <c r="D46" t="s">
         <v>236</v>
       </c>
-      <c r="D46" t="s">
-        <v>237</v>
-      </c>
       <c r="E46" t="s">
         <v>132</v>
       </c>
-      <c r="F46" s="25">
+      <c r="F46" s="22">
         <v>10050.07</v>
       </c>
       <c r="G46">
@@ -4373,21 +4367,21 @@
     </row>
     <row r="47" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
+        <v>237</v>
+      </c>
+      <c r="B47" t="s">
         <v>238</v>
       </c>
-      <c r="B47" t="s">
+      <c r="C47" t="s">
         <v>239</v>
       </c>
-      <c r="C47" t="s">
+      <c r="D47" t="s">
         <v>240</v>
       </c>
-      <c r="D47" t="s">
-        <v>241</v>
-      </c>
       <c r="E47" t="s">
         <v>132</v>
       </c>
-      <c r="F47" s="25">
+      <c r="F47" s="22">
         <v>9829.66</v>
       </c>
       <c r="G47">
@@ -4399,18 +4393,18 @@
         <v>90</v>
       </c>
       <c r="B48" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C48" t="s">
         <v>91</v>
       </c>
       <c r="D48" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E48" t="s">
         <v>132</v>
       </c>
-      <c r="F48" s="25">
+      <c r="F48" s="22">
         <v>8641.52</v>
       </c>
       <c r="G48">
@@ -4428,12 +4422,12 @@
         <v>109</v>
       </c>
       <c r="D49" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E49" t="s">
         <v>132</v>
       </c>
-      <c r="F49" s="25">
+      <c r="F49" s="22">
         <v>8639</v>
       </c>
       <c r="G49">
@@ -4442,21 +4436,21 @@
     </row>
     <row r="50" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
+        <v>244</v>
+      </c>
+      <c r="B50" t="s">
         <v>245</v>
       </c>
-      <c r="B50" t="s">
+      <c r="C50" t="s">
         <v>246</v>
       </c>
-      <c r="C50" t="s">
+      <c r="D50" t="s">
         <v>247</v>
       </c>
-      <c r="D50" t="s">
-        <v>248</v>
-      </c>
       <c r="E50" t="s">
         <v>132</v>
       </c>
-      <c r="F50" s="25">
+      <c r="F50" s="22">
         <v>8638.98</v>
       </c>
       <c r="G50">
@@ -4465,21 +4459,21 @@
     </row>
     <row r="51" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
+        <v>248</v>
+      </c>
+      <c r="B51" t="s">
         <v>249</v>
       </c>
-      <c r="B51" t="s">
+      <c r="C51" t="s">
         <v>250</v>
       </c>
-      <c r="C51" t="s">
+      <c r="D51" t="s">
         <v>251</v>
       </c>
-      <c r="D51" t="s">
-        <v>252</v>
-      </c>
       <c r="E51" t="s">
         <v>132</v>
       </c>
-      <c r="F51" s="25">
+      <c r="F51" s="22">
         <v>8472.8799999999992</v>
       </c>
       <c r="G51">
@@ -4488,21 +4482,21 @@
     </row>
     <row r="52" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
+        <v>252</v>
+      </c>
+      <c r="B52" t="s">
         <v>253</v>
       </c>
-      <c r="B52" t="s">
+      <c r="C52" t="s">
         <v>254</v>
       </c>
-      <c r="C52" t="s">
+      <c r="D52" t="s">
         <v>255</v>
       </c>
-      <c r="D52" t="s">
-        <v>256</v>
-      </c>
       <c r="E52" t="s">
         <v>132</v>
       </c>
-      <c r="F52" s="25">
+      <c r="F52" s="22">
         <v>8471.2000000000007</v>
       </c>
       <c r="G52">
@@ -4511,21 +4505,21 @@
     </row>
     <row r="53" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
+        <v>256</v>
+      </c>
+      <c r="B53" t="s">
         <v>257</v>
       </c>
-      <c r="B53" t="s">
+      <c r="C53" t="s">
         <v>258</v>
       </c>
-      <c r="C53" t="s">
+      <c r="D53" t="s">
         <v>259</v>
       </c>
-      <c r="D53" t="s">
-        <v>260</v>
-      </c>
       <c r="E53" t="s">
         <v>132</v>
       </c>
-      <c r="F53" s="25">
+      <c r="F53" s="22">
         <v>7624.57</v>
       </c>
       <c r="G53">
@@ -4534,21 +4528,21 @@
     </row>
     <row r="54" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
+        <v>260</v>
+      </c>
+      <c r="B54" t="s">
         <v>261</v>
       </c>
-      <c r="B54" t="s">
+      <c r="C54" t="s">
         <v>262</v>
       </c>
-      <c r="C54" t="s">
+      <c r="D54" t="s">
         <v>263</v>
       </c>
-      <c r="D54" t="s">
-        <v>264</v>
-      </c>
       <c r="E54" t="s">
         <v>132</v>
       </c>
-      <c r="F54" s="25">
+      <c r="F54" s="22">
         <v>7421.18</v>
       </c>
       <c r="G54">
@@ -4557,21 +4551,21 @@
     </row>
     <row r="55" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
+        <v>264</v>
+      </c>
+      <c r="B55" t="s">
         <v>265</v>
       </c>
-      <c r="B55" t="s">
+      <c r="C55" t="s">
         <v>266</v>
       </c>
-      <c r="C55" t="s">
+      <c r="D55" t="s">
         <v>267</v>
       </c>
-      <c r="D55" t="s">
-        <v>268</v>
-      </c>
       <c r="E55" t="s">
         <v>132</v>
       </c>
-      <c r="F55" s="25">
+      <c r="F55" s="22">
         <v>7284.72</v>
       </c>
       <c r="G55">
@@ -4580,21 +4574,21 @@
     </row>
     <row r="56" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
+        <v>268</v>
+      </c>
+      <c r="B56" t="s">
         <v>269</v>
       </c>
-      <c r="B56" t="s">
+      <c r="C56" t="s">
         <v>270</v>
       </c>
-      <c r="C56" t="s">
+      <c r="D56" t="s">
         <v>271</v>
       </c>
-      <c r="D56" t="s">
-        <v>272</v>
-      </c>
       <c r="E56" t="s">
         <v>132</v>
       </c>
-      <c r="F56" s="25">
+      <c r="F56" s="22">
         <v>7113.57</v>
       </c>
       <c r="G56">
@@ -4603,21 +4597,21 @@
     </row>
     <row r="57" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
+        <v>272</v>
+      </c>
+      <c r="B57" t="s">
         <v>273</v>
       </c>
-      <c r="B57" t="s">
+      <c r="C57" t="s">
         <v>274</v>
       </c>
-      <c r="C57" t="s">
+      <c r="D57" t="s">
         <v>275</v>
       </c>
-      <c r="D57" t="s">
-        <v>276</v>
-      </c>
       <c r="E57" t="s">
         <v>132</v>
       </c>
-      <c r="F57" s="25">
+      <c r="F57" s="22">
         <v>6777.96</v>
       </c>
       <c r="G57">
@@ -4626,21 +4620,21 @@
     </row>
     <row r="58" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
+        <v>276</v>
+      </c>
+      <c r="B58" t="s">
         <v>277</v>
       </c>
-      <c r="B58" t="s">
+      <c r="C58" t="s">
         <v>278</v>
       </c>
-      <c r="C58" t="s">
+      <c r="D58" t="s">
         <v>279</v>
       </c>
-      <c r="D58" t="s">
-        <v>280</v>
-      </c>
       <c r="E58" t="s">
         <v>132</v>
       </c>
-      <c r="F58" s="25">
+      <c r="F58" s="22">
         <v>6775.4</v>
       </c>
       <c r="G58">
@@ -4658,12 +4652,12 @@
         <v>106</v>
       </c>
       <c r="D59" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E59" t="s">
         <v>132</v>
       </c>
-      <c r="F59" s="25">
+      <c r="F59" s="22">
         <v>6438.99</v>
       </c>
       <c r="G59">
@@ -4681,12 +4675,12 @@
         <v>85</v>
       </c>
       <c r="D60" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E60" t="s">
         <v>132</v>
       </c>
-      <c r="F60" s="25">
+      <c r="F60" s="22">
         <v>5083.8999999999996</v>
       </c>
       <c r="G60">
@@ -4695,21 +4689,21 @@
     </row>
     <row r="61" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
+        <v>282</v>
+      </c>
+      <c r="B61" t="s">
         <v>283</v>
       </c>
-      <c r="B61" t="s">
+      <c r="C61" t="s">
         <v>284</v>
       </c>
-      <c r="C61" t="s">
+      <c r="D61" t="s">
         <v>285</v>
       </c>
-      <c r="D61" t="s">
-        <v>286</v>
-      </c>
       <c r="E61" t="s">
         <v>132</v>
       </c>
-      <c r="F61" s="25">
+      <c r="F61" s="22">
         <v>4575.42</v>
       </c>
       <c r="G61">
@@ -4727,12 +4721,12 @@
         <v>115</v>
       </c>
       <c r="D62" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E62" t="s">
         <v>132</v>
       </c>
-      <c r="F62" s="25">
+      <c r="F62" s="22">
         <v>4403.3999999999996</v>
       </c>
       <c r="G62">
@@ -4741,21 +4735,21 @@
     </row>
     <row r="63" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
+        <v>287</v>
+      </c>
+      <c r="B63" t="s">
         <v>288</v>
       </c>
-      <c r="B63" t="s">
+      <c r="C63" t="s">
         <v>289</v>
       </c>
-      <c r="C63" t="s">
+      <c r="D63" t="s">
         <v>290</v>
       </c>
-      <c r="D63" t="s">
-        <v>291</v>
-      </c>
       <c r="E63" t="s">
         <v>132</v>
       </c>
-      <c r="F63" s="25">
+      <c r="F63" s="22">
         <v>4021.2</v>
       </c>
       <c r="G63">
@@ -4767,18 +4761,18 @@
         <v>81</v>
       </c>
       <c r="B64" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C64" t="s">
         <v>82</v>
       </c>
       <c r="D64" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E64" t="s">
         <v>132</v>
       </c>
-      <c r="F64" s="25">
+      <c r="F64" s="22">
         <v>3982.2</v>
       </c>
       <c r="G64">
@@ -4787,21 +4781,21 @@
     </row>
     <row r="65" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
+        <v>293</v>
+      </c>
+      <c r="B65" t="s">
         <v>294</v>
       </c>
-      <c r="B65" t="s">
+      <c r="C65" t="s">
         <v>295</v>
       </c>
-      <c r="C65" t="s">
+      <c r="D65" t="s">
         <v>296</v>
       </c>
-      <c r="D65" t="s">
-        <v>297</v>
-      </c>
       <c r="E65" t="s">
         <v>132</v>
       </c>
-      <c r="F65" s="25">
+      <c r="F65" s="22">
         <v>3981.36</v>
       </c>
       <c r="G65">
@@ -4819,12 +4813,12 @@
         <v>118</v>
       </c>
       <c r="D66" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E66" t="s">
         <v>132</v>
       </c>
-      <c r="F66" s="25">
+      <c r="F66" s="22">
         <v>3302.54</v>
       </c>
       <c r="G66">
@@ -4833,21 +4827,21 @@
     </row>
     <row r="67" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
+        <v>298</v>
+      </c>
+      <c r="B67" t="s">
         <v>299</v>
       </c>
-      <c r="B67" t="s">
+      <c r="C67" t="s">
         <v>300</v>
       </c>
-      <c r="C67" t="s">
+      <c r="D67" t="s">
         <v>301</v>
       </c>
-      <c r="D67" t="s">
-        <v>302</v>
-      </c>
       <c r="E67" t="s">
         <v>132</v>
       </c>
-      <c r="F67" s="25">
+      <c r="F67" s="22">
         <v>3134.75</v>
       </c>
       <c r="G67">
@@ -4865,12 +4859,12 @@
         <v>97</v>
       </c>
       <c r="D68" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E68" t="s">
         <v>132</v>
       </c>
-      <c r="F68" s="25">
+      <c r="F68" s="22">
         <v>3007.62</v>
       </c>
       <c r="G68">
@@ -4888,12 +4882,12 @@
         <v>112</v>
       </c>
       <c r="D69" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E69" t="s">
         <v>132</v>
       </c>
-      <c r="F69" s="25">
+      <c r="F69" s="22">
         <v>2960.16</v>
       </c>
       <c r="G69">
@@ -4902,21 +4896,21 @@
     </row>
     <row r="70" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
+        <v>304</v>
+      </c>
+      <c r="B70" t="s">
         <v>305</v>
       </c>
-      <c r="B70" t="s">
+      <c r="C70" t="s">
         <v>306</v>
       </c>
-      <c r="C70" t="s">
+      <c r="D70" t="s">
         <v>307</v>
       </c>
-      <c r="D70" t="s">
-        <v>308</v>
-      </c>
       <c r="E70" t="s">
         <v>132</v>
       </c>
-      <c r="F70" s="25">
+      <c r="F70" s="22">
         <v>2795.76</v>
       </c>
       <c r="G70">
@@ -4925,21 +4919,21 @@
     </row>
     <row r="71" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
+        <v>308</v>
+      </c>
+      <c r="B71" t="s">
+        <v>294</v>
+      </c>
+      <c r="C71" t="s">
         <v>309</v>
       </c>
-      <c r="B71" t="s">
-        <v>295</v>
-      </c>
-      <c r="C71" t="s">
-        <v>310</v>
-      </c>
       <c r="D71" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E71" t="s">
         <v>132</v>
       </c>
-      <c r="F71" s="25">
+      <c r="F71" s="22">
         <v>1990.68</v>
       </c>
       <c r="G71">
@@ -4948,21 +4942,21 @@
     </row>
     <row r="72" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
+        <v>310</v>
+      </c>
+      <c r="B72" t="s">
         <v>311</v>
       </c>
-      <c r="B72" t="s">
+      <c r="C72" t="s">
         <v>312</v>
       </c>
-      <c r="C72" t="s">
+      <c r="D72" t="s">
         <v>313</v>
       </c>
-      <c r="D72" t="s">
-        <v>314</v>
-      </c>
       <c r="E72" t="s">
         <v>132</v>
       </c>
-      <c r="F72" s="25">
+      <c r="F72" s="22">
         <v>1694.07</v>
       </c>
       <c r="G72">
@@ -4971,21 +4965,21 @@
     </row>
     <row r="73" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B73" t="s">
         <v>122</v>
       </c>
       <c r="C73" t="s">
+        <v>315</v>
+      </c>
+      <c r="D73" t="s">
         <v>316</v>
       </c>
-      <c r="D73" t="s">
-        <v>317</v>
-      </c>
       <c r="E73" t="s">
         <v>132</v>
       </c>
-      <c r="F73" s="25">
+      <c r="F73" s="22">
         <v>1694.07</v>
       </c>
       <c r="G73">
@@ -5003,12 +4997,12 @@
         <v>103</v>
       </c>
       <c r="D74" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E74" t="s">
         <v>132</v>
       </c>
-      <c r="F74" s="25">
+      <c r="F74" s="22">
         <v>1609.32</v>
       </c>
       <c r="G74">
@@ -5017,21 +5011,21 @@
     </row>
     <row r="75" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
+        <v>318</v>
+      </c>
+      <c r="B75" t="s">
+        <v>277</v>
+      </c>
+      <c r="C75" t="s">
         <v>319</v>
       </c>
-      <c r="B75" t="s">
-        <v>278</v>
-      </c>
-      <c r="C75" t="s">
-        <v>320</v>
-      </c>
       <c r="D75" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E75" t="s">
         <v>132</v>
       </c>
-      <c r="F75" s="25">
+      <c r="F75" s="22">
         <v>1380.51</v>
       </c>
       <c r="G75">
@@ -5049,12 +5043,12 @@
         <v>128</v>
       </c>
       <c r="D76" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E76" t="s">
         <v>132</v>
       </c>
-      <c r="F76" s="25">
+      <c r="F76" s="22">
         <v>1143.22</v>
       </c>
       <c r="G76">
@@ -5063,21 +5057,21 @@
     </row>
     <row r="77" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
+        <v>321</v>
+      </c>
+      <c r="B77" t="s">
         <v>322</v>
       </c>
-      <c r="B77" t="s">
+      <c r="C77" t="s">
         <v>323</v>
       </c>
-      <c r="C77" t="s">
+      <c r="D77" t="s">
         <v>324</v>
       </c>
-      <c r="D77" t="s">
-        <v>325</v>
-      </c>
       <c r="E77" t="s">
         <v>132</v>
       </c>
-      <c r="F77" s="25">
+      <c r="F77" s="22">
         <v>761.02</v>
       </c>
       <c r="G77">
@@ -5086,21 +5080,21 @@
     </row>
     <row r="78" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
+        <v>325</v>
+      </c>
+      <c r="B78" t="s">
         <v>326</v>
       </c>
-      <c r="B78" t="s">
+      <c r="C78" t="s">
         <v>327</v>
       </c>
-      <c r="C78" t="s">
+      <c r="D78" t="s">
         <v>328</v>
       </c>
-      <c r="D78" t="s">
-        <v>329</v>
-      </c>
       <c r="E78" t="s">
         <v>132</v>
       </c>
-      <c r="F78" s="25">
+      <c r="F78" s="22">
         <v>719.5</v>
       </c>
       <c r="G78">
@@ -5109,21 +5103,21 @@
     </row>
     <row r="79" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
+        <v>329</v>
+      </c>
+      <c r="B79" t="s">
         <v>330</v>
       </c>
-      <c r="B79" t="s">
+      <c r="C79" t="s">
         <v>331</v>
       </c>
-      <c r="C79" t="s">
+      <c r="D79" t="s">
         <v>332</v>
       </c>
-      <c r="D79" t="s">
-        <v>333</v>
-      </c>
       <c r="E79" t="s">
         <v>132</v>
       </c>
-      <c r="F79" s="25">
+      <c r="F79" s="22">
         <v>677.12</v>
       </c>
       <c r="G79">
@@ -5141,12 +5135,12 @@
         <v>100</v>
       </c>
       <c r="D80" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E80" t="s">
         <v>132</v>
       </c>
-      <c r="F80" s="25">
+      <c r="F80" s="22">
         <v>0</v>
       </c>
       <c r="G80">
@@ -5164,12 +5158,12 @@
         <v>121</v>
       </c>
       <c r="D81" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E81" t="s">
         <v>132</v>
       </c>
-      <c r="F81" s="25">
+      <c r="F81" s="22">
         <v>0</v>
       </c>
       <c r="G81">
@@ -5178,21 +5172,21 @@
     </row>
     <row r="82" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
+        <v>335</v>
+      </c>
+      <c r="B82" t="s">
         <v>336</v>
       </c>
-      <c r="B82" t="s">
+      <c r="C82" t="s">
         <v>337</v>
       </c>
-      <c r="C82" t="s">
+      <c r="D82" t="s">
         <v>338</v>
       </c>
-      <c r="D82" t="s">
-        <v>339</v>
-      </c>
       <c r="E82" t="s">
         <v>132</v>
       </c>
-      <c r="F82" s="25">
+      <c r="F82" s="22">
         <v>0</v>
       </c>
       <c r="G82">
@@ -5201,21 +5195,21 @@
     </row>
     <row r="83" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
+        <v>339</v>
+      </c>
+      <c r="B83" t="s">
         <v>340</v>
       </c>
-      <c r="B83" t="s">
+      <c r="C83" t="s">
         <v>341</v>
       </c>
-      <c r="C83" t="s">
+      <c r="D83" t="s">
         <v>342</v>
       </c>
-      <c r="D83" t="s">
-        <v>343</v>
-      </c>
       <c r="E83" t="s">
         <v>132</v>
       </c>
-      <c r="F83" s="25">
+      <c r="F83" s="22">
         <v>0</v>
       </c>
       <c r="G83">
@@ -5224,21 +5218,21 @@
     </row>
     <row r="84" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
+        <v>343</v>
+      </c>
+      <c r="B84" t="s">
         <v>344</v>
       </c>
-      <c r="B84" t="s">
+      <c r="C84" t="s">
         <v>345</v>
       </c>
-      <c r="C84" t="s">
+      <c r="D84" t="s">
         <v>346</v>
       </c>
-      <c r="D84" t="s">
-        <v>347</v>
-      </c>
       <c r="E84" t="s">
         <v>132</v>
       </c>
-      <c r="F84" s="25">
+      <c r="F84" s="22">
         <v>0</v>
       </c>
       <c r="G84">
@@ -5256,12 +5250,12 @@
         <v>94</v>
       </c>
       <c r="D85" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E85" t="s">
         <v>132</v>
       </c>
-      <c r="F85" s="25">
+      <c r="F85" s="22">
         <v>0</v>
       </c>
       <c r="G85">
@@ -5270,21 +5264,21 @@
     </row>
     <row r="86" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
+        <v>348</v>
+      </c>
+      <c r="B86" t="s">
         <v>349</v>
       </c>
-      <c r="B86" t="s">
+      <c r="C86" t="s">
         <v>350</v>
       </c>
-      <c r="C86" t="s">
+      <c r="D86" t="s">
         <v>351</v>
       </c>
-      <c r="D86" t="s">
-        <v>352</v>
-      </c>
       <c r="E86" t="s">
         <v>132</v>
       </c>
-      <c r="F86" s="25">
+      <c r="F86" s="22">
         <v>0</v>
       </c>
       <c r="G86">
@@ -5293,21 +5287,21 @@
     </row>
     <row r="87" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
+        <v>134</v>
+      </c>
+      <c r="B87" t="s">
+        <v>136</v>
+      </c>
+      <c r="C87" t="s">
         <v>135</v>
       </c>
-      <c r="B87" t="s">
-        <v>137</v>
-      </c>
-      <c r="C87" t="s">
-        <v>136</v>
-      </c>
       <c r="D87" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E87" t="s">
         <v>132</v>
       </c>
-      <c r="F87" s="25">
+      <c r="F87" s="22">
         <v>0</v>
       </c>
       <c r="G87">
@@ -5316,21 +5310,21 @@
     </row>
     <row r="88" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
+        <v>353</v>
+      </c>
+      <c r="B88" t="s">
         <v>354</v>
       </c>
-      <c r="B88" t="s">
+      <c r="C88" t="s">
         <v>355</v>
       </c>
-      <c r="C88" t="s">
+      <c r="D88" t="s">
         <v>356</v>
       </c>
-      <c r="D88" t="s">
-        <v>357</v>
-      </c>
       <c r="E88" t="s">
         <v>132</v>
       </c>
-      <c r="F88" s="25">
+      <c r="F88" s="22">
         <v>0</v>
       </c>
       <c r="G88">
@@ -5348,12 +5342,12 @@
         <v>131</v>
       </c>
       <c r="D89" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E89" t="s">
         <v>132</v>
       </c>
-      <c r="F89" s="25">
+      <c r="F89" s="22">
         <v>0</v>
       </c>
       <c r="G89">
@@ -5362,21 +5356,21 @@
     </row>
     <row r="90" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
+        <v>358</v>
+      </c>
+      <c r="B90" t="s">
         <v>359</v>
       </c>
-      <c r="B90" t="s">
+      <c r="C90" t="s">
         <v>360</v>
       </c>
-      <c r="C90" t="s">
+      <c r="D90" t="s">
         <v>361</v>
       </c>
-      <c r="D90" t="s">
-        <v>362</v>
-      </c>
       <c r="E90" t="s">
         <v>132</v>
       </c>
-      <c r="F90" s="25">
+      <c r="F90" s="22">
         <v>0</v>
       </c>
       <c r="G90">
@@ -5385,21 +5379,21 @@
     </row>
     <row r="91" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
+        <v>362</v>
+      </c>
+      <c r="B91" t="s">
         <v>363</v>
       </c>
-      <c r="B91" t="s">
+      <c r="C91" t="s">
         <v>364</v>
       </c>
-      <c r="C91" t="s">
+      <c r="D91" t="s">
         <v>365</v>
       </c>
-      <c r="D91" t="s">
-        <v>366</v>
-      </c>
       <c r="E91" t="s">
         <v>132</v>
       </c>
-      <c r="F91" s="25">
+      <c r="F91" s="22">
         <v>0</v>
       </c>
       <c r="G91">
@@ -5704,233 +5698,233 @@
       <c r="AA1" s="5"/>
     </row>
     <row r="2" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="21">
+      <c r="D2" s="18">
         <v>1</v>
       </c>
-      <c r="E2" s="22">
+      <c r="E2" s="19">
         <v>2415.25</v>
       </c>
-      <c r="F2" s="19" t="s">
-        <v>132</v>
-      </c>
-      <c r="G2" s="18" t="s">
-        <v>370</v>
+      <c r="F2" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="G2" s="15" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="3" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="20" t="s">
+        <v>206</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>208</v>
+      </c>
+      <c r="C3" s="13" t="s">
         <v>207</v>
       </c>
-      <c r="B3" s="18" t="s">
-        <v>209</v>
-      </c>
-      <c r="C3" s="15" t="s">
-        <v>208</v>
-      </c>
-      <c r="D3" s="15">
+      <c r="D3" s="13">
         <v>1</v>
       </c>
-      <c r="E3" s="22">
+      <c r="E3" s="19">
         <v>2542.37</v>
       </c>
-      <c r="F3" s="19" t="s">
-        <v>132</v>
-      </c>
-      <c r="G3" s="18" t="s">
-        <v>370</v>
+      <c r="F3" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="G3" s="15" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="4" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="D4" s="15">
+      <c r="D4" s="13">
         <v>1</v>
       </c>
-      <c r="E4" s="22">
+      <c r="E4" s="19">
         <v>1398.31</v>
       </c>
-      <c r="F4" s="19" t="s">
-        <v>132</v>
-      </c>
-      <c r="G4" s="18" t="s">
-        <v>370</v>
+      <c r="F4" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="G4" s="15" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="5" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="23" t="s">
+      <c r="A5" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="15">
+      <c r="D5" s="13">
         <v>1</v>
       </c>
-      <c r="E5" s="22">
+      <c r="E5" s="19">
         <v>3114.41</v>
       </c>
-      <c r="F5" s="19" t="s">
-        <v>132</v>
-      </c>
-      <c r="G5" s="18" t="s">
-        <v>370</v>
+      <c r="F5" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="G5" s="15" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="6" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="D6" s="15">
+      <c r="D6" s="13">
         <v>1</v>
       </c>
-      <c r="E6" s="22">
+      <c r="E6" s="19">
         <v>2987.29</v>
       </c>
-      <c r="F6" s="19" t="s">
-        <v>132</v>
-      </c>
-      <c r="G6" s="18" t="s">
-        <v>370</v>
+      <c r="F6" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="G6" s="15" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="7" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="23" t="s">
+      <c r="A7" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="C7" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="D7" s="15">
+      <c r="D7" s="13">
         <v>1</v>
       </c>
-      <c r="E7" s="22">
+      <c r="E7" s="19">
         <v>2415.25</v>
       </c>
-      <c r="F7" s="19" t="s">
-        <v>132</v>
-      </c>
-      <c r="G7" s="18" t="s">
-        <v>370</v>
+      <c r="F7" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="G7" s="15" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="8" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="20" t="s">
+      <c r="A8" s="17" t="s">
+        <v>310</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>312</v>
+      </c>
+      <c r="C8" s="13" t="s">
         <v>311</v>
       </c>
-      <c r="B8" s="18" t="s">
-        <v>313</v>
-      </c>
-      <c r="C8" s="15" t="s">
-        <v>312</v>
-      </c>
-      <c r="D8" s="15">
+      <c r="D8" s="13">
         <v>1</v>
       </c>
-      <c r="E8" s="22">
+      <c r="E8" s="19">
         <v>1271.19</v>
       </c>
-      <c r="F8" s="19" t="s">
-        <v>132</v>
-      </c>
-      <c r="G8" s="18" t="s">
-        <v>370</v>
+      <c r="F8" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="G8" s="15" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="9" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="23" t="s">
+      <c r="A9" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>204</v>
+      </c>
+      <c r="C9" s="13" t="s">
         <v>203</v>
       </c>
-      <c r="B9" s="18" t="s">
-        <v>205</v>
-      </c>
-      <c r="C9" s="15" t="s">
-        <v>204</v>
-      </c>
-      <c r="D9" s="15">
+      <c r="D9" s="13">
         <v>1</v>
       </c>
-      <c r="E9" s="22">
+      <c r="E9" s="19">
         <v>762.71</v>
       </c>
-      <c r="F9" s="19" t="s">
-        <v>132</v>
-      </c>
-      <c r="G9" s="18" t="s">
-        <v>370</v>
+      <c r="F9" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="G9" s="15" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="10" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="17" t="s">
-        <v>134</v>
-      </c>
-      <c r="B10" s="18" t="s">
-        <v>373</v>
+      <c r="A10" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>372</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="15">
+      <c r="D10" s="13">
         <v>1</v>
       </c>
-      <c r="E10" s="22">
+      <c r="E10" s="19">
         <v>5719.71</v>
       </c>
-      <c r="F10" s="19" t="s">
-        <v>132</v>
-      </c>
-      <c r="G10" s="18" t="s">
+      <c r="F10" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="G10" s="15" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="11" t="s">
         <v>371</v>
       </c>
-    </row>
-    <row r="11" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>372</v>
-      </c>
-      <c r="D11" s="15">
+      <c r="D11" s="13">
         <v>1</v>
       </c>
-      <c r="E11" s="17">
+      <c r="E11" s="14">
         <v>14935</v>
       </c>
-      <c r="F11" s="19" t="s">
-        <v>132</v>
-      </c>
-      <c r="G11" s="18" t="s">
-        <v>371</v>
+      <c r="F11" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="G11" s="15" t="s">
+        <v>370</v>
       </c>
     </row>
     <row r="12" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
